--- a/Output/heterog_terciles_migration_lapop_stata.xlsx
+++ b/Output/heterog_terciles_migration_lapop_stata.xlsx
@@ -13,15 +13,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="38" uniqueCount="22">
   <si>
     <t>tercile_var</t>
   </si>
   <si>
-    <t>t_en_pareja</t>
-  </si>
-  <si>
-    <t>t_interes_pol_mucho</t>
+    <t>t_alt_pre_avg</t>
+  </si>
+  <si>
+    <t>t_density_2010</t>
+  </si>
+  <si>
+    <t>t_fem_2010</t>
+  </si>
+  <si>
+    <t>t_izam_pre_avg</t>
+  </si>
+  <si>
+    <t>t_mean_schyr_2010</t>
+  </si>
+  <si>
+    <t>t_med_dage_2010</t>
+  </si>
+  <si>
+    <t>t_pea_2010</t>
+  </si>
+  <si>
+    <t>t_unemp_2010</t>
   </si>
   <si>
     <t>tercile</t>
@@ -106,7 +124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -114,43 +132,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -161,40 +179,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>0.026874948846612401</v>
+        <v>0.0017588074644499</v>
       </c>
       <c r="D2" s="1">
-        <v>0.044580541551113129</v>
+        <v>0.036940798163414002</v>
       </c>
       <c r="E2" s="1">
-        <v>0.5466148853302002</v>
+        <v>0.96202588081359863</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.060475662350654602</v>
+        <v>0.08542034775018692</v>
       </c>
       <c r="G2" s="1">
-        <v>0.12779325246810913</v>
+        <v>0.11724564433097839</v>
       </c>
       <c r="H2" s="1">
-        <v>0.63604873418807983</v>
+        <v>0.46627157926559448</v>
       </c>
       <c r="I2" s="1">
-        <v>0.6047249908357526</v>
+        <v>0.56656045064457883</v>
       </c>
       <c r="J2" s="1">
-        <v>2556</v>
+        <v>2324</v>
       </c>
       <c r="K2" s="1">
-        <v>0.12806824410791301</v>
+        <v>0.1305931438454648</v>
       </c>
       <c r="L2" s="1">
-        <v>0.49315068125724793</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1">
-        <v>0.089056906742263006</v>
+        <v>0.92774541759234197</v>
       </c>
       <c r="N2" s="1">
-        <v>0.34060835838317871</v>
+        <v>0.90024691820144653</v>
       </c>
     </row>
     <row r="3">
@@ -205,40 +223,40 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>0.043428806317242302</v>
+        <v>0.0214626146686571</v>
       </c>
       <c r="D3" s="1">
-        <v>0.023802556097507477</v>
+        <v>0.039749655872583389</v>
       </c>
       <c r="E3" s="1">
-        <v>0.068069905042648316</v>
+        <v>0.58923518657684326</v>
       </c>
       <c r="F3" s="1">
-        <v>0.031714461743831635</v>
+        <v>0.090981669723987579</v>
       </c>
       <c r="G3" s="1">
-        <v>0.1052175834774971</v>
+        <v>0.16420711576938629</v>
       </c>
       <c r="H3" s="1">
-        <v>0.76309585571289063</v>
+        <v>0.57953327894210816</v>
       </c>
       <c r="I3" s="1">
-        <v>0.92578809702071974</v>
+        <v>0.72969285795492766</v>
       </c>
       <c r="J3" s="1">
-        <v>3103</v>
+        <v>2797</v>
       </c>
       <c r="K3" s="1">
-        <v>0.159886052280901</v>
+        <v>0.13081000518204289</v>
       </c>
       <c r="L3" s="1">
-        <v>0.54570639133453369</v>
+        <v>40</v>
       </c>
       <c r="M3" s="1">
-        <v>0.089056906742263006</v>
+        <v>0.92774541759234197</v>
       </c>
       <c r="N3" s="1">
-        <v>0.34060835838317871</v>
+        <v>0.90024691820144653</v>
       </c>
     </row>
     <row r="4">
@@ -249,40 +267,40 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.072281065675532399</v>
+        <v>0.00056959814715809999</v>
       </c>
       <c r="D4" s="1">
-        <v>0.047043614089488983</v>
+        <v>0.071666240692138672</v>
       </c>
       <c r="E4" s="1">
-        <v>0.12442333996295929</v>
+        <v>0.99365854263305664</v>
       </c>
       <c r="F4" s="1">
-        <v>0.24383048713207245</v>
+        <v>-0.029799137264490128</v>
       </c>
       <c r="G4" s="1">
-        <v>0.16469711065292358</v>
+        <v>0.23742906749248505</v>
       </c>
       <c r="H4" s="1">
-        <v>0.13874565064907074</v>
+        <v>0.90012174844741821</v>
       </c>
       <c r="I4" s="1">
-        <v>0.12601686924492439</v>
+        <v>0.92101003612705168</v>
       </c>
       <c r="J4" s="1">
-        <v>1753</v>
+        <v>2327</v>
       </c>
       <c r="K4" s="1">
-        <v>0.1272747622059123</v>
+        <v>0.1544096356280438</v>
       </c>
       <c r="L4" s="1">
-        <v>0.68493151664733887</v>
+        <v>100</v>
       </c>
       <c r="M4" s="1">
-        <v>0.089056906742263006</v>
+        <v>0.92774541759234197</v>
       </c>
       <c r="N4" s="1">
-        <v>0.34060835838317871</v>
+        <v>0.90024691820144653</v>
       </c>
     </row>
     <row r="5">
@@ -293,40 +311,40 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.031311117148157902</v>
+        <v>0.021303635045358801</v>
       </c>
       <c r="D5" s="1">
-        <v>0.053136970847845078</v>
+        <v>0.045514989644289017</v>
       </c>
       <c r="E5" s="1">
-        <v>0.55569159984588623</v>
+        <v>0.63974344730377197</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.1413760632276535</v>
+        <v>-0.089971311390399933</v>
       </c>
       <c r="G5" s="1">
-        <v>0.27254778146743775</v>
+        <v>0.40195551514625549</v>
       </c>
       <c r="H5" s="1">
-        <v>0.60395580530166626</v>
+        <v>0.82288646697998047</v>
       </c>
       <c r="I5" s="1">
-        <v>0.69642281554523444</v>
+        <v>0.75689485856696614</v>
       </c>
       <c r="J5" s="1">
-        <v>1936</v>
+        <v>696</v>
       </c>
       <c r="K5" s="1">
-        <v>0.14992559525035329</v>
+        <v>0.1611914365572292</v>
       </c>
       <c r="L5" s="1">
-        <v>0.097222223877906799</v>
+        <v>6.730000019099764</v>
       </c>
       <c r="M5" s="1">
-        <v>0.060445601166383499</v>
+        <v>0.1418795378646808</v>
       </c>
       <c r="N5" s="1">
-        <v>0.57763963937759399</v>
+        <v>0.1387307345867157</v>
       </c>
     </row>
     <row r="6">
@@ -337,40 +355,40 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>0.0348200665577547</v>
+        <v>0.17969049598521031</v>
       </c>
       <c r="D6" s="1">
-        <v>0.014198217540979385</v>
+        <v>0.084127306938171387</v>
       </c>
       <c r="E6" s="1">
-        <v>0.014189686626195908</v>
+        <v>0.032684680074453354</v>
       </c>
       <c r="F6" s="1">
-        <v>0.14458967745304108</v>
+        <v>-0.81816059350967407</v>
       </c>
       <c r="G6" s="1">
-        <v>0.062435735017061234</v>
+        <v>0.44156035780906677</v>
       </c>
       <c r="H6" s="1">
-        <v>0.020568311214447021</v>
+        <v>0.063898831605911255</v>
       </c>
       <c r="I6" s="1">
-        <v>0.14219960906687951</v>
+        <v>0.057447770136797798</v>
       </c>
       <c r="J6" s="1">
-        <v>2841</v>
+        <v>1079</v>
       </c>
       <c r="K6" s="1">
-        <v>0.1477451779360959</v>
+        <v>0.15720814207609829</v>
       </c>
       <c r="L6" s="1">
-        <v>0.15753424167633059</v>
+        <v>21.379999161016912</v>
       </c>
       <c r="M6" s="1">
-        <v>0.060445601166383499</v>
+        <v>0.1418795378646808</v>
       </c>
       <c r="N6" s="1">
-        <v>0.57763963937759399</v>
+        <v>0.1387307345867157</v>
       </c>
     </row>
     <row r="7">
@@ -381,40 +399,832 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.075567918432986297</v>
+        <v>-0.0077102385023290997</v>
       </c>
       <c r="D7" s="1">
-        <v>0.050077199935913086</v>
+        <v>0.044886831194162369</v>
       </c>
       <c r="E7" s="1">
-        <v>0.13129152357578278</v>
+        <v>0.86361783742904663</v>
       </c>
       <c r="F7" s="1">
-        <v>0.0949835404753685</v>
+        <v>0.094828978180885315</v>
       </c>
       <c r="G7" s="1">
-        <v>0.1431882381439209</v>
+        <v>0.13866801559925079</v>
       </c>
       <c r="H7" s="1">
-        <v>0.50710809230804443</v>
+        <v>0.49406597018241882</v>
       </c>
       <c r="I7" s="1">
-        <v>0.37251467070472061</v>
+        <v>0.57137333583414673</v>
       </c>
       <c r="J7" s="1">
-        <v>2635</v>
+        <v>5673</v>
       </c>
       <c r="K7" s="1">
-        <v>0.13269625756494641</v>
+        <v>0.1300720416105727</v>
       </c>
       <c r="L7" s="1">
-        <v>0.2777777910232544</v>
+        <v>14596.959960953391</v>
       </c>
       <c r="M7" s="1">
-        <v>0.060445601166383499</v>
+        <v>0.1418795378646808</v>
       </c>
       <c r="N7" s="1">
-        <v>0.57763963937759399</v>
+        <v>0.1387307345867157</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.017132227935435299</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.034831594675779343</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.62281912565231323</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.14212316274642944</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.18016023933887482</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.43018746376037598</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.55819359033843252</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1057</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.19224879688176091</v>
+      </c>
+      <c r="L8" s="1">
+        <v>50.124210357666023</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.66331129624361229</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.79782885313034058</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>-0.041622406732063202</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.055526763200759888</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.45350056886672974</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.24353510141372681</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.32807719707489014</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.4578993022441864</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.44243440661141858</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1738</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.13754545081091241</v>
+      </c>
+      <c r="L9" s="1">
+        <v>51.011665344238281</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.66331129624361229</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.79782885313034058</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.0076518885107689002</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.04484812542796135</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.86452430486679077</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.03607722744345665</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.13935671746730805</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.79572474956512451</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.87573694791651158</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4653</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.1281121422968847</v>
+      </c>
+      <c r="L10" s="1">
+        <v>53.967708587646477</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.66331129624361229</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.79782885313034058</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.019569745198600899</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.062802836298942566</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.75533992052078247</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-0.037227131426334381</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.21484903991222382</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.86243832111358643</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.83644931339773554</v>
+      </c>
+      <c r="J11" s="1">
+        <v>3303</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.15264978396767359</v>
+      </c>
+      <c r="L11" s="1">
+        <v>58.032534286520473</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0.98672228631554681</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.82492178678512573</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.017620783683208401</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.03323093056678772</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.59593689441680908</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.096499592065811157</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.11248233169317245</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.39094278216362</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.5681912739730195</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1596</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.11521993547968661</v>
+      </c>
+      <c r="L12" s="1">
+        <v>67.910022936735004</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0.98672228631554681</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.82492178678512573</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.0261851677793302</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.041065406054258347</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.52370452880859375</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.018124410882592201</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.14317753911018372</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.89926731586456299</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.96393933001526755</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2549</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.13004246448249129</v>
+      </c>
+      <c r="L13" s="1">
+        <v>84.28643396228712</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0.98672228631554681</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.82492178678512573</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.052433166964293503</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.017113342881202698</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.0021848923061043024</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.022888984531164169</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.061209287494421005</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.70844429731369019</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.69995567297785555</v>
+      </c>
+      <c r="J14" s="1">
+        <v>950</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.20225377007585171</v>
+      </c>
+      <c r="L14" s="1">
+        <v>7.1263031959533692</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0.0014660040294467</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.030623137950897217</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-0.11542950309319169</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.050273966044187546</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.021675340831279755</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.0767557621002197</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.42212182283401489</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.010747057385742664</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.0107110090044602</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1807</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.12351075359455189</v>
+      </c>
+      <c r="L15" s="1">
+        <v>7.918515682220459</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0.0014660040294467</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0.030623137950897217</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <v>-0.046411639339188397</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.043634824454784393</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.28749290108680725</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.17889818549156189</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.13087029755115509</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.17162895202636719</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.19136723679730541</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4691</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.13231007853707419</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10.923336029052731</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0.0014660040294467</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.030623137950897217</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>-0.029273423840226701</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.054604507982730866</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.59189009666442871</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.44026169180870056</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.30235376954078674</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.14536097645759583</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.1874844847119411</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1520</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.17379366954213121</v>
+      </c>
+      <c r="L17" s="1">
+        <v>26</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.098519724196397596</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0.32157203555107117</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.057608305919601699</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.0316941998898983</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.069120794534683228</v>
+      </c>
+      <c r="F18" s="1">
+        <v>-0.152144655585289</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.26023343205451965</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.55878520011901856</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.45498259755332621</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3109</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.12691238272680519</v>
+      </c>
+      <c r="L18" s="1">
+        <v>30</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0.098519724196397596</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0.32157203555107117</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>-0.076507026789201405</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.061988338828086853</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.21712227165699005</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.17157779633998871</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.20374618470668793</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.3997233510017395</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.34630425113127072</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2819</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0.13999163599260259</v>
+      </c>
+      <c r="L19" s="1">
+        <v>38</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0.098519724196397596</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0.32157203555107117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.053964998557635098</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.019330287352204323</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.0052426601760089397</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.17319165170192719</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.15016317367553711</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.24876414239406586</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.36990092204797198</v>
+      </c>
+      <c r="J20" s="1">
+        <v>860</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0.17936112856228639</v>
+      </c>
+      <c r="L20" s="1">
+        <v>58.098484039306641</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0.27142349991864922</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0.67119777202606201</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>-0.036230848921681803</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.12455780059099197</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.77114629745483399</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.51574039459228516</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.7149164080619812</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.47066372632980347</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.51070607558428804</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1374</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0.1745746449736629</v>
+      </c>
+      <c r="L21" s="1">
+        <v>65.748924255371094</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0.27142349991864922</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0.67119777202606201</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>-0.016381770783899002</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.04307861253619194</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.70374041795730591</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.042257927358150482</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.12253795564174652</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.73020273447036743</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.7183383515892986</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5214</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0.1251160504906311</v>
+      </c>
+      <c r="L22" s="1">
+        <v>72.977546691894531</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0.27142349991864922</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0.67119777202606201</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
+        <v>-0.022423453347060699</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.15303716063499451</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.88350862264633179</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.2892301082611084</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.7994874119758606</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.71752434968948364</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.7433352349473854</v>
+      </c>
+      <c r="J23" s="1">
+        <v>788</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.18547645136691171</v>
+      </c>
+      <c r="L23" s="1">
+        <v>2.6501767635345459</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0.93074526153865</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0.79588019847869873</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>-0.016542630540902902</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.037864454090595245</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.66219055652618408</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.036922875791788101</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.12468024343252182</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.76712274551391602</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0.73972711390174084</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2125</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.12937879595867971</v>
+      </c>
+      <c r="L24" s="1">
+        <v>3.662563800811768</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.93074526153865</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0.79588019847869873</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.0033774857016901998</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.03919711709022522</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.93133389949798584</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.14618512988090515</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.12041550129652023</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.2247454971075058</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0.35602569846938242</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4535</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0.1372014207788799</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5.4402060508728027</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0.93074526153865</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0.79588019847869873</v>
       </c>
     </row>
   </sheetData>
